--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-precondition-extension.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-precondition-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
